--- a/usuarios.csv.xlsx
+++ b/usuarios.csv.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VISUAL CODE\cobro luz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DC78B4F-4426-4826-95DF-833D2205E8A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CBEE838-EC96-41D3-98F7-7EEE34C5E106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -774,6 +774,7 @@
     <col min="1" max="1" width="20.77734375" customWidth="1"/>
     <col min="3" max="3" width="14.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.77734375" customWidth="1"/>
+    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -812,6 +813,9 @@
       <c r="E2" t="s">
         <v>9</v>
       </c>
+      <c r="F2">
+        <v>948148546</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">

--- a/usuarios.csv.xlsx
+++ b/usuarios.csv.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VISUAL CODE\cobro luz\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VISUAL CODE\SISTEMA DE COBRO DE LUZ 4 ENERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CBEE838-EC96-41D3-98F7-7EEE34C5E106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{445AF50A-8690-439B-843D-CD8F69598C09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -457,8 +457,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -486,8 +494,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -772,8 +781,9 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.77734375" customWidth="1"/>
-    <col min="3" max="3" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.77734375" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" customWidth="1"/>
+    <col min="4" max="4" width="39.109375" customWidth="1"/>
+    <col min="5" max="5" width="16.21875" customWidth="1"/>
     <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -867,6 +877,9 @@
       <c r="E5" t="s">
         <v>15</v>
       </c>
+      <c r="F5">
+        <v>926433019</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -884,6 +897,7 @@
       <c r="E6" t="s">
         <v>17</v>
       </c>
+      <c r="F6" s="1"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -901,6 +915,9 @@
       <c r="E7" t="s">
         <v>19</v>
       </c>
+      <c r="F7">
+        <v>969572753</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -1055,7 +1072,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -1072,7 +1089,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>6</v>
       </c>
@@ -1089,7 +1106,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -1106,7 +1123,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -1123,7 +1140,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -1140,7 +1157,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -1157,7 +1174,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -1174,7 +1191,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -1191,7 +1208,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>52</v>
       </c>
@@ -1208,7 +1225,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>52</v>
       </c>
@@ -1225,7 +1242,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>52</v>
       </c>
@@ -1242,7 +1259,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>52</v>
       </c>
@@ -1259,7 +1276,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>52</v>
       </c>
@@ -1276,7 +1293,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>52</v>
       </c>
@@ -1292,8 +1309,11 @@
       <c r="E30" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F30">
+        <v>969955598</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>52</v>
       </c>
@@ -1309,8 +1329,9 @@
       <c r="E31" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F31" s="1"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>52</v>
       </c>
@@ -1599,7 +1620,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>52</v>
       </c>
@@ -1616,7 +1637,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>52</v>
       </c>
@@ -1632,8 +1653,11 @@
       <c r="E50" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F50">
+        <v>902468595</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>52</v>
       </c>
@@ -1650,7 +1674,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>52</v>
       </c>
@@ -1667,7 +1691,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>52</v>
       </c>
@@ -1684,7 +1708,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>52</v>
       </c>
@@ -1701,7 +1725,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>52</v>
       </c>
@@ -1718,7 +1742,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>52</v>
       </c>
@@ -1735,7 +1759,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>52</v>
       </c>
@@ -1752,7 +1776,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>52</v>
       </c>
@@ -1769,7 +1793,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>52</v>
       </c>
@@ -1786,7 +1810,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>52</v>
       </c>
@@ -1803,7 +1827,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>52</v>
       </c>
@@ -1820,7 +1844,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>52</v>
       </c>
@@ -1837,7 +1861,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>52</v>
       </c>
@@ -1854,7 +1878,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>52</v>
       </c>

--- a/usuarios.csv.xlsx
+++ b/usuarios.csv.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VISUAL CODE\SISTEMA DE COBRO DE LUZ 4 ENERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{445AF50A-8690-439B-843D-CD8F69598C09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B8966E3-8F93-46AD-8266-D70E53775320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,9 +30,6 @@
     <t>Nombre</t>
   </si>
   <si>
-    <t>Lectura_Anterior</t>
-  </si>
-  <si>
     <t>Calle</t>
   </si>
   <si>
@@ -451,6 +448,9 @@
   </si>
   <si>
     <t>2375.60</t>
+  </si>
+  <si>
+    <t>Lectura_Anterior_Junio</t>
   </si>
 </sst>
 </file>
@@ -783,45 +783,45 @@
     <col min="1" max="1" width="20.77734375" customWidth="1"/>
     <col min="3" max="3" width="8.88671875" customWidth="1"/>
     <col min="4" max="4" width="39.109375" customWidth="1"/>
-    <col min="5" max="5" width="16.21875" customWidth="1"/>
+    <col min="5" max="5" width="21.77734375" customWidth="1"/>
     <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>3</v>
-      </c>
-      <c r="C1" t="s">
-        <v>4</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
       </c>
       <c r="E1" t="s">
-        <v>1</v>
+        <v>141</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
         <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
       </c>
       <c r="F2">
         <v>948148546</v>
@@ -829,53 +829,53 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
         <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
       <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
         <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
         <v>14</v>
-      </c>
-      <c r="E5" t="s">
-        <v>15</v>
       </c>
       <c r="F5">
         <v>926433019</v>
@@ -883,37 +883,37 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6">
         <v>5</v>
       </c>
       <c r="D6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s">
         <v>16</v>
-      </c>
-      <c r="E6" t="s">
-        <v>17</v>
       </c>
       <c r="F6" s="1"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7">
         <v>6</v>
       </c>
       <c r="D7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s">
         <v>18</v>
-      </c>
-      <c r="E7" t="s">
-        <v>19</v>
       </c>
       <c r="F7">
         <v>969572753</v>
@@ -921,393 +921,393 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8">
         <v>7</v>
       </c>
       <c r="D8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" t="s">
         <v>20</v>
-      </c>
-      <c r="E8" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9">
         <v>8</v>
       </c>
       <c r="D9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" t="s">
         <v>22</v>
-      </c>
-      <c r="E9" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C10">
         <v>9</v>
       </c>
       <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" t="s">
         <v>24</v>
-      </c>
-      <c r="E10" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C11">
         <v>10</v>
       </c>
       <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
         <v>26</v>
-      </c>
-      <c r="E11" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C12">
         <v>11</v>
       </c>
       <c r="D12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" t="s">
         <v>28</v>
-      </c>
-      <c r="E12" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C13">
         <v>12</v>
       </c>
       <c r="D13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" t="s">
         <v>30</v>
-      </c>
-      <c r="E13" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14">
         <v>13</v>
       </c>
       <c r="D14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" t="s">
         <v>32</v>
-      </c>
-      <c r="E14" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C15">
         <v>14</v>
       </c>
       <c r="D15" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" t="s">
         <v>34</v>
-      </c>
-      <c r="E15" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C16">
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B17" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C17">
         <v>16</v>
       </c>
       <c r="D17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" t="s">
         <v>37</v>
-      </c>
-      <c r="E17" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C18">
         <v>17</v>
       </c>
       <c r="D18" t="s">
+        <v>38</v>
+      </c>
+      <c r="E18" t="s">
         <v>39</v>
-      </c>
-      <c r="E18" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C19">
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B20" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C20">
         <v>19</v>
       </c>
       <c r="D20" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20" t="s">
         <v>42</v>
-      </c>
-      <c r="E20" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B21" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C21">
         <v>20</v>
       </c>
       <c r="D21" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" t="s">
         <v>44</v>
-      </c>
-      <c r="E21" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B22" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C22">
         <v>21</v>
       </c>
       <c r="D22" t="s">
+        <v>45</v>
+      </c>
+      <c r="E22" t="s">
         <v>46</v>
-      </c>
-      <c r="E22" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B23" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C23">
         <v>22</v>
       </c>
       <c r="D23" t="s">
+        <v>47</v>
+      </c>
+      <c r="E23" t="s">
         <v>48</v>
-      </c>
-      <c r="E23" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B24" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C24">
         <v>23</v>
       </c>
       <c r="D24" t="s">
+        <v>49</v>
+      </c>
+      <c r="E24" t="s">
         <v>50</v>
-      </c>
-      <c r="E24" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B25" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C25">
         <v>23</v>
       </c>
       <c r="D25" t="s">
+        <v>52</v>
+      </c>
+      <c r="E25" t="s">
         <v>53</v>
-      </c>
-      <c r="E25" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B26" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C26">
         <v>24</v>
       </c>
       <c r="D26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B27" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C27">
         <v>25</v>
       </c>
       <c r="D27" t="s">
+        <v>55</v>
+      </c>
+      <c r="E27" t="s">
         <v>56</v>
-      </c>
-      <c r="E27" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B28" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C28">
         <v>26</v>
       </c>
       <c r="D28" t="s">
+        <v>57</v>
+      </c>
+      <c r="E28" t="s">
         <v>58</v>
-      </c>
-      <c r="E28" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B29" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C29">
         <v>27</v>
       </c>
       <c r="D29" t="s">
+        <v>59</v>
+      </c>
+      <c r="E29" t="s">
         <v>60</v>
-      </c>
-      <c r="E29" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B30" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C30">
         <v>28</v>
       </c>
       <c r="D30" t="s">
+        <v>61</v>
+      </c>
+      <c r="E30" t="s">
         <v>62</v>
-      </c>
-      <c r="E30" t="s">
-        <v>63</v>
       </c>
       <c r="F30">
         <v>969955598</v>
@@ -1315,343 +1315,343 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B31" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C31">
         <v>29</v>
       </c>
       <c r="D31" t="s">
+        <v>63</v>
+      </c>
+      <c r="E31" t="s">
         <v>64</v>
-      </c>
-      <c r="E31" t="s">
-        <v>65</v>
       </c>
       <c r="F31" s="1"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B32" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C32">
         <v>30</v>
       </c>
       <c r="D32" t="s">
+        <v>65</v>
+      </c>
+      <c r="E32" t="s">
         <v>66</v>
-      </c>
-      <c r="E32" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B33" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C33">
         <v>31</v>
       </c>
       <c r="D33" t="s">
+        <v>67</v>
+      </c>
+      <c r="E33" t="s">
         <v>68</v>
-      </c>
-      <c r="E33" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B34" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C34">
         <v>32</v>
       </c>
       <c r="D34" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B35" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C35">
         <v>33</v>
       </c>
       <c r="D35" t="s">
+        <v>70</v>
+      </c>
+      <c r="E35" t="s">
         <v>71</v>
-      </c>
-      <c r="E35" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B36" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C36">
         <v>34</v>
       </c>
       <c r="D36" t="s">
+        <v>72</v>
+      </c>
+      <c r="E36" t="s">
         <v>73</v>
-      </c>
-      <c r="E36" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B37" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C37">
         <v>35</v>
       </c>
       <c r="D37" t="s">
+        <v>74</v>
+      </c>
+      <c r="E37" t="s">
         <v>75</v>
-      </c>
-      <c r="E37" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B38" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C38">
         <v>36</v>
       </c>
       <c r="D38" t="s">
+        <v>76</v>
+      </c>
+      <c r="E38" t="s">
         <v>77</v>
-      </c>
-      <c r="E38" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B39" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C39">
         <v>37</v>
       </c>
       <c r="D39" t="s">
+        <v>78</v>
+      </c>
+      <c r="E39" t="s">
         <v>79</v>
-      </c>
-      <c r="E39" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B40" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C40">
         <v>38</v>
       </c>
       <c r="D40" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E40" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B41" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C41">
         <v>39</v>
       </c>
       <c r="D41" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E41" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B42" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C42">
         <v>40</v>
       </c>
       <c r="D42" t="s">
+        <v>82</v>
+      </c>
+      <c r="E42" t="s">
         <v>83</v>
-      </c>
-      <c r="E42" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B43" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C43">
         <v>41</v>
       </c>
       <c r="D43" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E43" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B44" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C44">
         <v>42</v>
       </c>
       <c r="D44" t="s">
+        <v>85</v>
+      </c>
+      <c r="E44" t="s">
         <v>86</v>
-      </c>
-      <c r="E44" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B45" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C45">
         <v>43</v>
       </c>
       <c r="D45" t="s">
+        <v>87</v>
+      </c>
+      <c r="E45" t="s">
         <v>88</v>
-      </c>
-      <c r="E45" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C46">
         <v>44</v>
       </c>
       <c r="D46" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E46" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B47" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C47">
         <v>45</v>
       </c>
       <c r="D47" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E47" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B48" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C48">
         <v>1</v>
       </c>
       <c r="D48" t="s">
+        <v>92</v>
+      </c>
+      <c r="E48" t="s">
         <v>93</v>
-      </c>
-      <c r="E48" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B49" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C49">
         <v>2</v>
       </c>
       <c r="D49" t="s">
+        <v>94</v>
+      </c>
+      <c r="E49" t="s">
         <v>95</v>
-      </c>
-      <c r="E49" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C50">
         <v>3</v>
       </c>
       <c r="D50" t="s">
+        <v>96</v>
+      </c>
+      <c r="E50" t="s">
         <v>97</v>
-      </c>
-      <c r="E50" t="s">
-        <v>98</v>
       </c>
       <c r="F50">
         <v>902468595</v>
@@ -1659,393 +1659,393 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B51" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C51">
         <v>4</v>
       </c>
       <c r="D51" t="s">
+        <v>98</v>
+      </c>
+      <c r="E51" t="s">
         <v>99</v>
-      </c>
-      <c r="E51" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C52">
         <v>5</v>
       </c>
       <c r="D52" t="s">
+        <v>100</v>
+      </c>
+      <c r="E52" t="s">
         <v>101</v>
-      </c>
-      <c r="E52" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C53">
         <v>6</v>
       </c>
       <c r="D53" t="s">
+        <v>102</v>
+      </c>
+      <c r="E53" t="s">
         <v>103</v>
-      </c>
-      <c r="E53" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B54" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C54">
         <v>7</v>
       </c>
       <c r="D54" t="s">
+        <v>104</v>
+      </c>
+      <c r="E54" t="s">
         <v>105</v>
-      </c>
-      <c r="E54" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B55" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C55">
         <v>8</v>
       </c>
       <c r="D55" t="s">
+        <v>106</v>
+      </c>
+      <c r="E55" t="s">
         <v>107</v>
-      </c>
-      <c r="E55" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B56" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C56">
         <v>9</v>
       </c>
       <c r="D56" t="s">
+        <v>108</v>
+      </c>
+      <c r="E56" t="s">
         <v>109</v>
-      </c>
-      <c r="E56" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B57" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C57">
         <v>10</v>
       </c>
       <c r="D57" t="s">
+        <v>110</v>
+      </c>
+      <c r="E57" t="s">
         <v>111</v>
-      </c>
-      <c r="E57" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B58" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C58">
         <v>11</v>
       </c>
       <c r="D58" t="s">
+        <v>112</v>
+      </c>
+      <c r="E58" t="s">
         <v>113</v>
-      </c>
-      <c r="E58" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B59" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C59">
         <v>12</v>
       </c>
       <c r="D59" t="s">
+        <v>114</v>
+      </c>
+      <c r="E59" t="s">
         <v>115</v>
-      </c>
-      <c r="E59" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B60" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C60">
         <v>13</v>
       </c>
       <c r="D60" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E60" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B61" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C61">
         <v>14</v>
       </c>
       <c r="D61" t="s">
+        <v>117</v>
+      </c>
+      <c r="E61" t="s">
         <v>118</v>
-      </c>
-      <c r="E61" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B62" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C62">
         <v>15</v>
       </c>
       <c r="D62" t="s">
+        <v>119</v>
+      </c>
+      <c r="E62" t="s">
         <v>120</v>
-      </c>
-      <c r="E62" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B63" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C63">
         <v>16</v>
       </c>
       <c r="D63" t="s">
+        <v>121</v>
+      </c>
+      <c r="E63" t="s">
         <v>122</v>
-      </c>
-      <c r="E63" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B64" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C64">
         <v>17</v>
       </c>
       <c r="D64" t="s">
+        <v>123</v>
+      </c>
+      <c r="E64" t="s">
         <v>124</v>
-      </c>
-      <c r="E64" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B65" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C65">
         <v>18</v>
       </c>
       <c r="D65" t="s">
+        <v>125</v>
+      </c>
+      <c r="E65" t="s">
         <v>126</v>
-      </c>
-      <c r="E65" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B66" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C66">
         <v>19</v>
       </c>
       <c r="D66" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E66" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B67" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C67">
         <v>20</v>
       </c>
       <c r="D67" t="s">
+        <v>128</v>
+      </c>
+      <c r="E67" t="s">
         <v>129</v>
-      </c>
-      <c r="E67" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B68" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C68">
         <v>21</v>
       </c>
       <c r="D68" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E68" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B69" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C69">
         <v>22</v>
       </c>
       <c r="D69" t="s">
+        <v>131</v>
+      </c>
+      <c r="E69" t="s">
         <v>132</v>
-      </c>
-      <c r="E69" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B70" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C70">
         <v>23</v>
       </c>
       <c r="D70" t="s">
+        <v>133</v>
+      </c>
+      <c r="E70" t="s">
         <v>134</v>
-      </c>
-      <c r="E70" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B71" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C71">
         <v>24</v>
       </c>
       <c r="D71" t="s">
+        <v>135</v>
+      </c>
+      <c r="E71" t="s">
         <v>136</v>
-      </c>
-      <c r="E71" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B72" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C72">
         <v>25</v>
       </c>
       <c r="D72" t="s">
+        <v>137</v>
+      </c>
+      <c r="E72" t="s">
         <v>138</v>
-      </c>
-      <c r="E72" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B73" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C73">
         <v>26</v>
       </c>
       <c r="D73" t="s">
+        <v>139</v>
+      </c>
+      <c r="E73" t="s">
         <v>140</v>
-      </c>
-      <c r="E73" t="s">
-        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/usuarios.csv.xlsx
+++ b/usuarios.csv.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VISUAL CODE\SISTEMA DE COBRO DE LUZ 4 ENERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CFE108B-26D6-47E4-AEC1-E10008EDEDD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E51CB98A-5F58-46BB-8129-137BC77F73D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -270,16 +270,16 @@
     <t>MORI CHUJUTALLI FRANKLIN</t>
   </si>
   <si>
-    <t>Lectura_Anterior_Junio</t>
-  </si>
-  <si>
     <t>Lectura_Anterior_Julio</t>
   </si>
   <si>
-    <t>Lectura_Anterior_Mayo</t>
-  </si>
-  <si>
-    <t>Lectura_Anterior_Abril</t>
+    <t>Lectura_Abril</t>
+  </si>
+  <si>
+    <t>Lectura_Mayo</t>
+  </si>
+  <si>
+    <t>Lectura_Junio</t>
   </si>
 </sst>
 </file>
@@ -647,16 +647,16 @@
         <v>0</v>
       </c>
       <c r="E1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F1" t="s">
         <v>83</v>
       </c>
       <c r="G1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H1" t="s">
         <v>81</v>
-      </c>
-      <c r="H1" t="s">
-        <v>82</v>
       </c>
       <c r="K1" t="s">
         <v>4</v>

--- a/usuarios.csv.xlsx
+++ b/usuarios.csv.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VISUAL CODE\SISTEMA DE COBRO DE LUZ 4 ENERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E51CB98A-5F58-46BB-8129-137BC77F73D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C358BB1-0C09-4A1C-BAE3-897FE8867D94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -270,9 +270,6 @@
     <t>MORI CHUJUTALLI FRANKLIN</t>
   </si>
   <si>
-    <t>Lectura_Anterior_Julio</t>
-  </si>
-  <si>
     <t>Lectura_Abril</t>
   </si>
   <si>
@@ -280,6 +277,9 @@
   </si>
   <si>
     <t>Lectura_Junio</t>
+  </si>
+  <si>
+    <t>Lectura_Julio</t>
   </si>
 </sst>
 </file>
@@ -622,18 +622,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K73"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.77734375" customWidth="1"/>
     <col min="3" max="3" width="8.88671875" customWidth="1"/>
     <col min="4" max="4" width="39.109375" customWidth="1"/>
     <col min="5" max="5" width="21.6640625" customWidth="1"/>
-    <col min="6" max="10" width="21.77734375" customWidth="1"/>
-    <col min="11" max="11" width="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.77734375" customWidth="1"/>
+    <col min="7" max="7" width="13.77734375" customWidth="1"/>
+    <col min="8" max="8" width="13.33203125" customWidth="1"/>
+    <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -647,22 +649,22 @@
         <v>0</v>
       </c>
       <c r="E1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1" t="s">
         <v>82</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>83</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>84</v>
       </c>
-      <c r="H1" t="s">
-        <v>81</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="I1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>30</v>
       </c>
@@ -688,7 +690,7 @@
         <v>1205.4000000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>30</v>
       </c>
@@ -714,7 +716,7 @@
         <v>111.6</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>30</v>
       </c>
@@ -739,11 +741,11 @@
       <c r="H4" s="2">
         <v>828.8</v>
       </c>
-      <c r="K4">
+      <c r="I4">
         <v>902468595</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -769,7 +771,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>30</v>
       </c>
@@ -795,7 +797,7 @@
         <v>1340.8</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -821,7 +823,7 @@
         <v>151.1</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -847,7 +849,7 @@
         <v>222.8</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -873,7 +875,7 @@
         <v>623.20000000000005</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -899,7 +901,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -925,7 +927,7 @@
         <v>250.8</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -951,7 +953,7 @@
         <v>322.60000000000002</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -977,7 +979,7 @@
         <v>115.2</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>30</v>
       </c>
@@ -1003,7 +1005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -1029,7 +1031,7 @@
         <v>1712.1</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -1055,7 +1057,7 @@
         <v>1282.5999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -1081,7 +1083,7 @@
         <v>1291.5</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>30</v>
       </c>
@@ -1107,7 +1109,7 @@
         <v>814.3</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>30</v>
       </c>
@@ -1133,7 +1135,7 @@
         <v>1378.9</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>30</v>
       </c>
@@ -1159,7 +1161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -1185,7 +1187,7 @@
         <v>456.4</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -1211,7 +1213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -1237,7 +1239,7 @@
         <v>179.3</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>30</v>
       </c>
@@ -1263,7 +1265,7 @@
         <v>35.9</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>30</v>
       </c>
@@ -1289,7 +1291,7 @@
         <v>535.70000000000005</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>30</v>
       </c>
@@ -1315,7 +1317,7 @@
         <v>687.6</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -1341,7 +1343,7 @@
         <v>2478.1</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>5</v>
       </c>
@@ -1364,11 +1366,11 @@
       <c r="H28" s="2">
         <v>1061.4000000000001</v>
       </c>
-      <c r="K28">
+      <c r="I28">
         <v>948148546</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -1392,7 +1394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>5</v>
       </c>
@@ -1416,7 +1418,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>5</v>
       </c>
@@ -1439,11 +1441,11 @@
       <c r="H31" s="2">
         <v>865.4</v>
       </c>
-      <c r="K31">
+      <c r="I31">
         <v>926433019</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>5</v>
       </c>
@@ -1466,9 +1468,9 @@
       <c r="H32" s="2">
         <v>168.4</v>
       </c>
-      <c r="K32" s="1"/>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="I32" s="1"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>5</v>
       </c>
@@ -1491,11 +1493,11 @@
       <c r="H33" s="2">
         <v>363.7</v>
       </c>
-      <c r="K33">
+      <c r="I33">
         <v>969572753</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>5</v>
       </c>
@@ -1519,7 +1521,7 @@
         <v>12.53</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>5</v>
       </c>
@@ -1543,7 +1545,7 @@
         <v>118.6</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>5</v>
       </c>
@@ -1567,7 +1569,7 @@
         <v>167.2</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>5</v>
       </c>
@@ -1591,7 +1593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>5</v>
       </c>
@@ -1615,7 +1617,7 @@
         <v>54.7</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>5</v>
       </c>
@@ -1639,7 +1641,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>5</v>
       </c>
@@ -1663,7 +1665,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>5</v>
       </c>
@@ -1687,7 +1689,7 @@
         <v>2335.3000000000002</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>5</v>
       </c>
@@ -1711,7 +1713,7 @@
         <v>53.1</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>5</v>
       </c>
@@ -1735,7 +1737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>5</v>
       </c>
@@ -1759,7 +1761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>5</v>
       </c>
@@ -1783,7 +1785,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>5</v>
       </c>
@@ -1807,7 +1809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>5</v>
       </c>
@@ -1831,7 +1833,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>5</v>
       </c>
@@ -1855,7 +1857,7 @@
         <v>113.1</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>5</v>
       </c>
@@ -1879,7 +1881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>5</v>
       </c>
@@ -1903,7 +1905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>30</v>
       </c>
@@ -1927,7 +1929,7 @@
         <v>43.7</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>30</v>
       </c>
@@ -1951,7 +1953,7 @@
         <v>117.9</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>30</v>
       </c>
@@ -1975,7 +1977,7 @@
         <v>1579.7</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>30</v>
       </c>
@@ -1999,7 +2001,7 @@
         <v>1454.7</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>30</v>
       </c>
@@ -2023,7 +2025,7 @@
         <v>105.3</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>30</v>
       </c>
@@ -2046,11 +2048,11 @@
       <c r="H56" s="2">
         <v>203.4</v>
       </c>
-      <c r="K56">
+      <c r="I56">
         <v>969955598</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>30</v>
       </c>
@@ -2073,9 +2075,9 @@
       <c r="H57" s="2">
         <v>76.099999999999994</v>
       </c>
-      <c r="K57" s="1"/>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="I57" s="1"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>30</v>
       </c>
@@ -2099,7 +2101,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>30</v>
       </c>
@@ -2123,7 +2125,7 @@
         <v>1246.8</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>30</v>
       </c>
@@ -2147,7 +2149,7 @@
         <v>2050.5</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>30</v>
       </c>
@@ -2171,7 +2173,7 @@
         <v>823.9</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>30</v>
       </c>
@@ -2195,7 +2197,7 @@
         <v>156.69999999999999</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>30</v>
       </c>
@@ -2219,7 +2221,7 @@
         <v>149.6</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>30</v>
       </c>
